--- a/file/test/Data.xlsx
+++ b/file/test/Data.xlsx
@@ -2295,9 +2295,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>978480</xdr:colOff>
+      <xdr:colOff>978120</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>165240</xdr:rowOff>
+      <xdr:rowOff>164880</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2306,7 +2306,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6686280" y="1118160"/>
-        <a:ext cx="1780200" cy="1279800"/>
+        <a:ext cx="1779840" cy="1279440"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2325,9 +2325,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>1005480</xdr:colOff>
+      <xdr:colOff>1005120</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>170280</xdr:rowOff>
+      <xdr:rowOff>169920</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2336,7 +2336,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="8670240" y="1309320"/>
-        <a:ext cx="1946520" cy="1651680"/>
+        <a:ext cx="1946160" cy="1651320"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2355,9 +2355,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>803160</xdr:colOff>
+      <xdr:colOff>802800</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>160560</xdr:rowOff>
+      <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2366,7 +2366,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="12634560" y="202680"/>
-        <a:ext cx="3233520" cy="4609080"/>
+        <a:ext cx="3233160" cy="4608720"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2374,6 +2374,50 @@
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>43200</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>28440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>267120</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>137880</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Image 1"/>
+        <xdr:cNvPicPr/>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId5"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6719040" y="3191400"/>
+          <a:ext cx="2222280" cy="2342160"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="0">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>

--- a/file/test/Data.xlsx
+++ b/file/test/Data.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" dateCompatibility="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\simonedagostino\workspace\cimo\one_workspace\file\test\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC16B1AD-7163-4C51-BEDE-149F7B52FDBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="21312" yWindow="1320" windowWidth="19620" windowHeight="12120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId5"/>
-    <pivotCache cacheId="2" r:id="rId6"/>
-    <pivotCache cacheId="3" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId2"/>
+    <pivotCache cacheId="1" r:id="rId3"/>
+    <pivotCache cacheId="2" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -25,374 +30,193 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="119">
-  <si>
-    <t xml:space="preserve">Id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Last Name</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gender</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dulce</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abril</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">United States</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15/10/2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count - Gender*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count - Country*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count - Age*</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mara</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hashimoto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Great Britain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16/08/2016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">France</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21/05/2015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kathleen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hanner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Result</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nereida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Magwood</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gaston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Brumm</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Etta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hurn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Earlean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Melgar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vincenza</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weiland</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fallon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Winward</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arcelia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bouska</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Franklyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unknow</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sherron</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ascencio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marcel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zabriskie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hazelton</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavonne</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Benito</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lauralee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Perrine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loreta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curren</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teresa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Strawn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Belinda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Partain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Holly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eudy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Many</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cuccia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Libbie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dalby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lester</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prothro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Marvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angelyn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vong</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Francesca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Beaudreau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Garth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gangi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carla</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trumbull</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Veta</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Muntz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stasia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Becker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jona</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grindle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Judie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Claywell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dewitt</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Borger</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hacker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kelsie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wachtel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pfau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shanice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mccrystal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chase</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Karner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tommie</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Underdahl</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dorcas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Darity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Angel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sanor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Willodean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Harn</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weston</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Martina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lafollette</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Felisa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Demetria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abbey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jeromy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Danz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rasheeda</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alkire</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="59">
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Country</t>
+  </si>
+  <si>
+    <t>Age</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Dulce</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>15/10/2017</t>
+  </si>
+  <si>
+    <t>Count - Gender*</t>
+  </si>
+  <si>
+    <t>Count - Country*</t>
+  </si>
+  <si>
+    <t>Count - Age*</t>
+  </si>
+  <si>
+    <t>Mara</t>
+  </si>
+  <si>
+    <t>Hashimoto</t>
+  </si>
+  <si>
+    <t>Great Britain</t>
+  </si>
+  <si>
+    <t>16/08/2016</t>
+  </si>
+  <si>
+    <t>France</t>
+  </si>
+  <si>
+    <t>Philip</t>
+  </si>
+  <si>
+    <t>Gent</t>
+  </si>
+  <si>
+    <t>Male</t>
+  </si>
+  <si>
+    <t>21/05/2015</t>
+  </si>
+  <si>
+    <t>Kathleen</t>
+  </si>
+  <si>
+    <t>Hanner</t>
+  </si>
+  <si>
+    <t>Total Result</t>
+  </si>
+  <si>
+    <t>Nereida</t>
+  </si>
+  <si>
+    <t>Magwood</t>
+  </si>
+  <si>
+    <t>Gaston</t>
+  </si>
+  <si>
+    <t>Brumm</t>
+  </si>
+  <si>
+    <t>Etta</t>
+  </si>
+  <si>
+    <t>Hurn</t>
+  </si>
+  <si>
+    <t>Earlean</t>
+  </si>
+  <si>
+    <t>Melgar</t>
+  </si>
+  <si>
+    <t>Vincenza</t>
+  </si>
+  <si>
+    <t>Weiland</t>
+  </si>
+  <si>
+    <t>Fallon</t>
+  </si>
+  <si>
+    <t>Winward</t>
+  </si>
+  <si>
+    <t>Arcelia</t>
+  </si>
+  <si>
+    <t>Bouska</t>
+  </si>
+  <si>
+    <t>Franklyn</t>
+  </si>
+  <si>
+    <t>Unknow</t>
+  </si>
+  <si>
+    <t>Sherron</t>
+  </si>
+  <si>
+    <t>Ascencio</t>
+  </si>
+  <si>
+    <t>Marcel</t>
+  </si>
+  <si>
+    <t>Zabriskie</t>
+  </si>
+  <si>
+    <t>Kina</t>
+  </si>
+  <si>
+    <t>Hazelton</t>
+  </si>
+  <si>
+    <t>Shavonne</t>
+  </si>
+  <si>
+    <t>Pia</t>
+  </si>
+  <si>
+    <t>Shavon</t>
+  </si>
+  <si>
+    <t>Benito</t>
+  </si>
+  <si>
+    <t>Lauralee</t>
+  </si>
+  <si>
+    <t>Perrine</t>
+  </si>
+  <si>
+    <t>Loreta</t>
+  </si>
+  <si>
+    <t>Curren</t>
+  </si>
+  <si>
+    <t>Teresa</t>
+  </si>
+  <si>
+    <t>Strawn</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yy"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="mm/dd/yy"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Noto Sans JP"/>
@@ -400,29 +224,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -436,9 +245,15 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="DejaVu Sans"/>
+      <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="2">
@@ -450,204 +265,193 @@
     </fill>
   </fills>
   <borders count="10">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="medium"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
-      <bottom style="thin"/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="medium"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="medium"/>
-      <top style="thin"/>
-      <bottom style="medium"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="26">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
+  </cellStyleXfs>
+  <cellXfs count="16">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-  </cellStyleXfs>
-  <cellXfs count="17">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyBorder="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyBorder="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="6" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="5" applyBorder="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="22" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="21" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="25" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="24" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="9" xfId="23" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="4" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="12">
+  <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
-    <cellStyle name="Pivot Table Category" xfId="20"/>
-    <cellStyle name="Pivot Table Corner" xfId="21"/>
-    <cellStyle name="Pivot Table Field" xfId="22"/>
-    <cellStyle name="Pivot Table Result" xfId="23"/>
-    <cellStyle name="Pivot Table Title" xfId="24"/>
-    <cellStyle name="Pivot Table Value" xfId="25"/>
+    <cellStyle name="Pivot Table Category" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
+    <cellStyle name="Pivot Table Corner" xfId="2" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Pivot Table Field" xfId="3" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
+    <cellStyle name="Pivot Table Result" xfId="4" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
+    <cellStyle name="Pivot Table Title" xfId="5" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Pivot Table Value" xfId="6" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -706,18 +510,37 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF4B1F6F"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -731,32 +554,36 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:explosion val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-A164-4201-9883-B077BBBB54D9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="1"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ff420e"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-A164-4201-9883-B077BBBB54D9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -771,6 +598,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -779,10 +607,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-A164-4201-9883-B077BBBB54D9}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -797,6 +631,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -805,8 +640,20 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-A164-4201-9883-B077BBBB54D9}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
@@ -821,6 +668,7 @@
                     <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -829,6 +677,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
@@ -840,6 +689,9 @@
                 </a:ln>
               </c:spPr>
             </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -870,7 +722,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-A164-4201-9883-B077BBBB54D9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
       <c:spPr>
@@ -903,30 +769,40 @@
               <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -940,43 +816,53 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:explosion val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-802A-450E-A086-96B59D8CB8A9}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="004586"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-802A-450E-A086-96B59D8CB8A9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
-            <c:idx val="1"/>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FFD320"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
-          </c:dPt>
-          <c:dPt>
-            <c:idx val="2"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:srgbClr val="ffd320"/>
-              </a:solidFill>
-              <a:ln w="0">
-                <a:noFill/>
-              </a:ln>
-            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-802A-450E-A086-96B59D8CB8A9}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -991,6 +877,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -999,10 +886,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-802A-450E-A086-96B59D8CB8A9}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1017,6 +910,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1025,10 +919,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-802A-450E-A086-96B59D8CB8A9}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1043,6 +943,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1051,8 +952,20 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-802A-450E-A086-96B59D8CB8A9}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
@@ -1067,6 +980,7 @@
                     <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -1075,6 +989,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
@@ -1086,6 +1001,9 @@
                 </a:ln>
               </c:spPr>
             </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
             <c:strRef>
@@ -1122,7 +1040,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-802A-450E-A086-96B59D8CB8A9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
       <c:spPr>
@@ -1155,30 +1087,40 @@
               <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
   <c:lang val="en-US"/>
   <c:roundedCorners val="0"/>
+  <c:style val="2"/>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
     <c:plotArea>
+      <c:layout/>
       <c:pieChart>
         <c:varyColors val="1"/>
         <c:ser>
@@ -1192,9 +1134,9 @@
               <a:noFill/>
             </a:ln>
           </c:spPr>
-          <c:explosion val="0"/>
           <c:dPt>
             <c:idx val="0"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="004586"/>
@@ -1203,64 +1145,100 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="1"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="2"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ffd320"/>
+                <a:srgbClr val="FFD320"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="3"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="579d1c"/>
+                <a:srgbClr val="579D1C"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="4"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7e0021"/>
+                <a:srgbClr val="7E0021"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="5"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="83caff"/>
+                <a:srgbClr val="83CAFF"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="6"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="314004"/>
@@ -1269,64 +1247,100 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000D-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="7"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="aecf00"/>
+                <a:srgbClr val="AECF00"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000F-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="8"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4b1f6f"/>
+                <a:srgbClr val="4B1F6F"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000011-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="9"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff950e"/>
+                <a:srgbClr val="FF950E"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000013-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="10"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="c5000b"/>
+                <a:srgbClr val="C5000B"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000015-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="11"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="0084d1"/>
+                <a:srgbClr val="0084D1"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000017-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="12"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="004586"/>
@@ -1335,64 +1349,100 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000019-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="13"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff420e"/>
+                <a:srgbClr val="FF420E"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001B-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="14"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ffd320"/>
+                <a:srgbClr val="FFD320"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001D-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="15"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="579d1c"/>
+                <a:srgbClr val="579D1C"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000001F-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="16"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="7e0021"/>
+                <a:srgbClr val="7E0021"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000021-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="17"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="83caff"/>
+                <a:srgbClr val="83CAFF"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000023-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="18"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
                 <a:srgbClr val="314004"/>
@@ -1401,54 +1451,84 @@
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000025-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="19"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="aecf00"/>
+                <a:srgbClr val="AECF00"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000027-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="20"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="4b1f6f"/>
+                <a:srgbClr val="4B1F6F"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000029-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="21"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="ff950e"/>
+                <a:srgbClr val="FF950E"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002B-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dPt>
             <c:idx val="22"/>
+            <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="c5000b"/>
+                <a:srgbClr val="C5000B"/>
               </a:solidFill>
               <a:ln w="0">
                 <a:noFill/>
               </a:ln>
             </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000002D-EFC7-450B-9542-BA3DF8342A92}"/>
+              </c:ext>
+            </c:extLst>
           </c:dPt>
           <c:dLbls>
             <c:dLbl>
               <c:idx val="0"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1463,6 +1543,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1471,10 +1552,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1489,6 +1576,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1497,10 +1585,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="2"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1515,6 +1609,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1523,10 +1618,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="3"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1541,6 +1642,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1549,10 +1651,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000007-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="4"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1567,6 +1675,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1575,10 +1684,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="5"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1593,6 +1708,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1601,10 +1717,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="6"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1619,6 +1741,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1627,10 +1750,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="7"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1645,6 +1774,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1653,10 +1783,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000F-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="8"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1671,6 +1807,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1679,10 +1816,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000011-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="9"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1697,6 +1840,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1705,10 +1849,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000013-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="10"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1723,6 +1873,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1731,10 +1882,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000015-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="11"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1749,6 +1906,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1757,10 +1915,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000017-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="12"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1775,6 +1939,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1783,10 +1948,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000019-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="13"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1801,6 +1972,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1809,10 +1981,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001B-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="14"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1827,6 +2005,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1835,10 +2014,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001D-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="15"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1853,6 +2038,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1861,10 +2047,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000001F-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="16"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1879,6 +2071,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1887,10 +2080,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000021-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="17"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1905,6 +2104,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1913,10 +2113,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000023-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="18"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1931,6 +2137,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1939,10 +2146,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000025-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="19"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1957,6 +2170,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1965,10 +2179,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000027-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="20"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -1983,6 +2203,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -1991,10 +2212,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000029-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="21"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -2009,6 +2236,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -2017,10 +2245,16 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002B-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
             <c:dLbl>
               <c:idx val="22"/>
+              <c:spPr/>
               <c:txPr>
                 <a:bodyPr wrap="none"/>
                 <a:lstStyle/>
@@ -2035,6 +2269,7 @@
                       <a:ea typeface="DejaVu Sans"/>
                     </a:defRPr>
                   </a:pPr>
+                  <a:endParaRPr lang="ja-JP"/>
                 </a:p>
               </c:txPr>
               <c:dLblPos val="bestFit"/>
@@ -2043,8 +2278,20 @@
               <c:showCatName val="0"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
-              <c:separator> </c:separator>
+              <c:showBubbleSize val="1"/>
+              <c:extLst>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000002D-EFC7-450B-9542-BA3DF8342A92}"/>
+                </c:ext>
+              </c:extLst>
             </c:dLbl>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
             <c:txPr>
               <a:bodyPr wrap="none"/>
               <a:lstStyle/>
@@ -2059,6 +2306,7 @@
                     <a:ea typeface="DejaVu Sans"/>
                   </a:defRPr>
                 </a:pPr>
+                <a:endParaRPr lang="ja-JP"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="bestFit"/>
@@ -2067,6 +2315,7 @@
             <c:showCatName val="0"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
+            <c:showBubbleSize val="1"/>
             <c:separator> </c:separator>
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
@@ -2078,11 +2327,15 @@
                 </a:ln>
               </c:spPr>
             </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:strRef>
+            <c:numRef>
               <c:f>Sheet1!$P$3:$P$25</c:f>
-              <c:strCache>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
                 <c:ptCount val="23"/>
                 <c:pt idx="0">
                   <c:v>21</c:v>
@@ -2153,8 +2406,8 @@
                 <c:pt idx="22">
                   <c:v>58</c:v>
                 </c:pt>
-              </c:strCache>
-            </c:strRef>
+              </c:numCache>
+            </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -2234,7 +2487,21 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000002E-EFC7-450B-9542-BA3DF8342A92}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
       <c:spPr>
@@ -2267,25 +2534,32 @@
               <a:ea typeface="DejaVu Sans"/>
             </a:defRPr>
           </a:pPr>
+          <a:endParaRPr lang="ja-JP"/>
         </a:p>
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="zero"/>
+    <c:showDLblsOverMax val="1"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
-      <a:srgbClr val="ffffff"/>
+      <a:srgbClr val="FFFFFF"/>
     </a:solidFill>
     <a:ln w="0">
       <a:noFill/>
     </a:ln>
   </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
 </c:chartSpace>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
@@ -2299,14 +2573,20 @@
       <xdr:row>12</xdr:row>
       <xdr:rowOff>164880</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="1" name=""/>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="6686280" y="1118160"/>
-        <a:ext cx="1779840" cy="1279440"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2329,14 +2609,20 @@
       <xdr:row>15</xdr:row>
       <xdr:rowOff>169920</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2" name=""/>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="8670240" y="1309320"/>
-        <a:ext cx="1946160" cy="1651320"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2359,14 +2645,20 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>160200</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame>
+    <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name=""/>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="12634560" y="202680"/>
-        <a:ext cx="3233160" cy="4608720"/>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2379,23 +2671,29 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>43200</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>28440</xdr:rowOff>
+      <xdr:colOff>793477</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>51887</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>267120</xdr:colOff>
-      <xdr:row>29</xdr:row>
-      <xdr:rowOff>137880</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>102997</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>161326</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Image 1"/>
+        <xdr:cNvPr id="5" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr/>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip r:embed="rId4">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <a:extLst>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
               <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId5"/>
@@ -2406,8 +2704,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6719040" y="3191400"/>
-          <a:ext cx="2222280" cy="2342160"/>
+          <a:off x="7346677" y="3615702"/>
+          <a:ext cx="2181674" cy="2782301"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2424,7 +2722,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="100" createdVersion="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedDate="0" createdVersion="3" recordCount="100" xr:uid="{00000000-000A-0000-FFFF-FFFF01000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="E1:E101" sheet="Sheet1"/>
   </cacheSource>
@@ -2436,11 +2734,16 @@
       </sharedItems>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="100" createdVersion="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedDate="0" createdVersion="3" recordCount="100" xr:uid="{00000000-000A-0000-FFFF-FFFF02000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="F1:F101" sheet="Sheet1"/>
   </cacheSource>
@@ -2453,11 +2756,16 @@
       </sharedItems>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" recordCount="100" createdVersion="3">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedDate="0" createdVersion="3" recordCount="100" xr:uid="{00000000-000A-0000-FFFF-FFFF03000000}">
   <cacheSource type="worksheet">
     <worksheetSource ref="G1:G101" sheet="Sheet1"/>
   </cacheSource>
@@ -2490,6 +2798,11 @@
       </sharedItems>
     </cacheField>
   </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
 </pivotCacheDefinition>
 </file>
 
@@ -3409,10 +3722,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DataPilot1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="0" outlineData="0" compact="0" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000002000000}" name="DataPilot1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" itemPrintTitles="1" indent="0" compact="0" compactData="0">
   <location ref="J2:K5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
-    <pivotField axis="axisRow" dataField="1" compact="0" showAll="0" defaultSubtotal="0" outline="0">
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="2">
         <item x="0"/>
         <item x="1"/>
@@ -3424,32 +3737,35 @@
   </rowFields>
   <rowItems count="3">
     <i>
-      <x v="0"/>
+      <x/>
     </i>
     <i>
       <x v="1"/>
     </i>
     <i t="grand">
-      <x v="2"/>
+      <x v="1048832"/>
     </i>
   </rowItems>
   <colItems count="1">
-    <i t="grand">
-      <x v="0"/>
-    </i>
+    <i t="grand"/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count - Gender*" fld="0" subtotal="count" numFmtId="164"/>
+    <dataField name="Count - Gender*" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DataPilot2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="0" outlineData="0" compact="0" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000001000000}" name="DataPilot2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" itemPrintTitles="1" indent="0" compact="0" compactData="0">
   <location ref="M2:N6" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
-    <pivotField axis="axisRow" dataField="1" compact="0" showAll="0" defaultSubtotal="0" outline="0">
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="3">
         <item x="0"/>
         <item x="1"/>
@@ -3462,7 +3778,7 @@
   </rowFields>
   <rowItems count="4">
     <i>
-      <x v="0"/>
+      <x/>
     </i>
     <i>
       <x v="1"/>
@@ -3471,26 +3787,29 @@
       <x v="2"/>
     </i>
     <i t="grand">
-      <x v="3"/>
+      <x v="1048832"/>
     </i>
   </rowItems>
   <colItems count="1">
-    <i t="grand">
-      <x v="0"/>
-    </i>
+    <i t="grand"/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count - Country*" fld="0" subtotal="count" numFmtId="164"/>
+    <dataField name="Count - Country*" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="DataPilot3" cacheId="3" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" useAutoFormatting="0" itemPrintTitles="1" indent="0" outline="0" outlineData="0" compact="0" compactData="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{00000000-0007-0000-0000-000000000000}" name="DataPilot3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0" dataCaption="Values" showDrill="0" itemPrintTitles="1" indent="0" compact="0" compactData="0">
   <location ref="P2:Q26" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="1">
-    <pivotField axis="axisRow" dataField="1" compact="0" showAll="0" defaultSubtotal="0" outline="0">
+    <pivotField axis="axisRow" dataField="1" compact="0" outline="0" showAll="0" defaultSubtotal="0">
       <items count="23">
         <item x="0"/>
         <item x="1"/>
@@ -3523,7 +3842,7 @@
   </rowFields>
   <rowItems count="24">
     <i>
-      <x v="0"/>
+      <x/>
     </i>
     <i>
       <x v="1"/>
@@ -3592,72 +3911,75 @@
       <x v="22"/>
     </i>
     <i t="grand">
-      <x v="23"/>
+      <x v="1048832"/>
     </i>
   </rowItems>
   <colItems count="1">
-    <i t="grand">
-      <x v="0"/>
-    </i>
+    <i t="grand"/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count - Age*" fld="0" subtotal="count" numFmtId="164"/>
+    <dataField name="Count - Age*" fld="0" subtotal="count" baseField="0" baseItem="0"/>
   </dataFields>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
   <a:themeElements>
     <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="18a303"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="0369a3"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="a33e03"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8e03a3"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="c99c00"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="c9211e"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ee"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="551a8b"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
-        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
-        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Arial"/>
+        <a:ea typeface="DejaVu Sans"/>
+        <a:cs typeface="DejaVu Sans"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -3710,2888 +4032,1373 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AMP101"/>
-  <sheetFormatPr defaultColWidth="8.34375" defaultRowHeight="14.65" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.33203125" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.45"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="1" style="1" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="2" width="2.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="14.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="2" width="2.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="14.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="2.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="1" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="2" width="2.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1019" min="19" style="2" width="11.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16379" style="2" width="11.53"/>
+    <col min="1" max="8" width="11.5546875" style="1" customWidth="1"/>
+    <col min="9" max="9" width="2.5546875" customWidth="1"/>
+    <col min="10" max="10" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.33203125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="2.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.33203125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="14.6640625" style="1" customWidth="1"/>
+    <col min="15" max="15" width="2.5546875" customWidth="1"/>
+    <col min="16" max="17" width="11.5546875" style="1" customWidth="1"/>
+    <col min="18" max="18" width="2.5546875" customWidth="1"/>
+    <col min="19" max="1019" width="11.5546875" customWidth="1"/>
+    <col min="16379" max="16384" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="true" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3"/>
-      <c r="B1" s="4" t="s">
+    <row r="1" spans="1:1030" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="AMF1" s="2"/>
-      <c r="AMG1" s="2"/>
-      <c r="AMH1" s="2"/>
-      <c r="AMI1" s="2"/>
-      <c r="AMJ1" s="2"/>
-      <c r="AMK1" s="2"/>
-      <c r="AML1" s="2"/>
-      <c r="AMM1" s="2"/>
-      <c r="AMN1" s="2"/>
-      <c r="AMO1" s="2"/>
-      <c r="AMP1" s="2"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="I1"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="AMF1"/>
+      <c r="AMG1"/>
+      <c r="AMH1"/>
+      <c r="AMI1"/>
+      <c r="AMJ1"/>
+      <c r="AMK1"/>
+      <c r="AML1"/>
+      <c r="AMM1"/>
+      <c r="AMN1"/>
+      <c r="AMO1"/>
+      <c r="AMP1"/>
+    </row>
+    <row r="2" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="1">
         <v>1562</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="n">
+      <c r="G2" s="1">
         <v>32</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="N2" s="9" t="s">
+      <c r="N2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="P2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="Q2" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+    <row r="3" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="1">
         <v>1582</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="1" t="n">
+      <c r="G3" s="1">
         <v>25</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="J3" s="10" t="s">
+      <c r="J3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="11" t="n">
+      <c r="K3" s="10">
         <v>76</v>
       </c>
-      <c r="M3" s="10" t="s">
+      <c r="M3" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="N3" s="11" t="n">
+      <c r="N3" s="10">
         <v>24</v>
       </c>
-      <c r="P3" s="10" t="n">
+      <c r="P3" s="9">
         <v>21</v>
       </c>
-      <c r="Q3" s="11" t="n">
+      <c r="Q3" s="10">
         <v>2</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+    <row r="4" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="1">
         <v>2587</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1" t="n">
+      <c r="G4" s="1">
         <v>36</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="13" t="n">
+      <c r="K4" s="12">
         <v>24</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="M4" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="N4" s="14" t="n">
+      <c r="N4" s="13">
         <v>28</v>
       </c>
-      <c r="P4" s="12" t="n">
+      <c r="P4" s="11">
         <v>23</v>
       </c>
-      <c r="Q4" s="14" t="n">
+      <c r="Q4" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+    <row r="5" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="1">
         <v>3549</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="1" t="n">
+      <c r="G5" s="1">
         <v>25</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J5" s="15" t="s">
+      <c r="J5" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="K5" s="16" t="n">
+      <c r="K5" s="15">
         <v>100</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="13" t="n">
+      <c r="N5" s="12">
         <v>48</v>
       </c>
-      <c r="P5" s="12" t="n">
+      <c r="P5" s="11">
         <v>24</v>
       </c>
-      <c r="Q5" s="14" t="n">
+      <c r="Q5" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+    <row r="6" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="1">
         <v>2468</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="G6" s="1">
         <v>58</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="16" t="n">
+      <c r="N6" s="15">
         <v>100</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="11">
         <v>25</v>
       </c>
-      <c r="Q6" s="14" t="n">
+      <c r="Q6" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+    <row r="7" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="1">
         <v>2554</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="G7" s="1">
         <v>24</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="11">
         <v>26</v>
       </c>
-      <c r="Q7" s="14" t="n">
+      <c r="Q7" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+    <row r="8" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="1">
         <v>3598</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="G8" s="1">
         <v>56</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="P8" s="12" t="n">
+      <c r="P8" s="11">
         <v>27</v>
       </c>
-      <c r="Q8" s="14" t="n">
+      <c r="Q8" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+    <row r="9" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
         <v>8</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="1">
         <v>2456</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="1" t="n">
+      <c r="G9" s="1">
         <v>27</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="11">
         <v>28</v>
       </c>
-      <c r="Q9" s="14" t="n">
+      <c r="Q9" s="13">
         <v>10</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+    <row r="10" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
         <v>9</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="1">
         <v>6548</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="1" t="n">
+      <c r="G10" s="1">
         <v>40</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="11">
         <v>29</v>
       </c>
-      <c r="Q10" s="14" t="n">
+      <c r="Q10" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+    <row r="11" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
         <v>10</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="1">
         <v>5486</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G11" s="1" t="n">
+      <c r="G11" s="1">
         <v>28</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" s="11">
         <v>31</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+    <row r="12" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="1">
         <v>1258</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G12" s="1" t="n">
+      <c r="G12" s="1">
         <v>39</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="H12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P12" s="12" t="n">
+      <c r="P12" s="11">
         <v>32</v>
       </c>
-      <c r="Q12" s="14" t="n">
+      <c r="Q12" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+    <row r="13" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="1">
         <v>2579</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="1" t="n">
+      <c r="G13" s="1">
         <v>38</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="P13" s="12" t="n">
+      <c r="P13" s="11">
         <v>34</v>
       </c>
-      <c r="Q13" s="14" t="n">
+      <c r="Q13" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+    <row r="14" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
         <v>13</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="1">
         <v>3256</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G14" s="1" t="n">
+      <c r="G14" s="1">
         <v>32</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P14" s="12" t="n">
+      <c r="P14" s="11">
         <v>35</v>
       </c>
-      <c r="Q14" s="14" t="n">
+      <c r="Q14" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+    <row r="15" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
         <v>14</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="1">
         <v>2587</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="F15" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G15" s="1" t="n">
+      <c r="G15" s="1">
         <v>26</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="H15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P15" s="12" t="n">
+      <c r="P15" s="11">
         <v>36</v>
       </c>
-      <c r="Q15" s="14" t="n">
+      <c r="Q15" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+    <row r="16" spans="1:1030" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
         <v>15</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="1">
         <v>3259</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G16" s="1" t="n">
+      <c r="G16" s="1">
         <v>31</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P16" s="12" t="n">
+      <c r="P16" s="11">
         <v>37</v>
       </c>
-      <c r="Q16" s="14" t="n">
+      <c r="Q16" s="13">
         <v>8</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
         <v>16</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="1">
         <v>1546</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="1" t="n">
+      <c r="G17" s="1">
         <v>24</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P17" s="12" t="n">
+      <c r="P17" s="11">
         <v>38</v>
       </c>
-      <c r="Q17" s="14" t="n">
+      <c r="Q17" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
         <v>17</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="1">
         <v>3579</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="1" t="n">
+      <c r="G18" s="1">
         <v>39</v>
       </c>
-      <c r="H18" s="7" t="s">
+      <c r="H18" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I18" s="5"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="P18" s="12" t="n">
+      <c r="I18" s="4"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="P18" s="11">
         <v>39</v>
       </c>
-      <c r="Q18" s="14" t="n">
+      <c r="Q18" s="13">
         <v>8</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
         <v>18</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="1">
         <v>6597</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G19" s="1" t="n">
+      <c r="G19" s="1">
         <v>28</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="P19" s="12" t="n">
+      <c r="P19" s="11">
         <v>40</v>
       </c>
-      <c r="Q19" s="14" t="n">
+      <c r="Q19" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
         <v>19</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="1">
         <v>9654</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="E20" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G20" s="1" t="n">
+      <c r="G20" s="1">
         <v>26</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="H20" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P20" s="12" t="n">
+      <c r="P20" s="11">
         <v>41</v>
       </c>
-      <c r="Q20" s="14" t="n">
+      <c r="Q20" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
         <v>20</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="1">
         <v>3569</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="E21" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="1" t="n">
+      <c r="G21" s="1">
         <v>46</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="H21" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="P21" s="12" t="n">
+      <c r="P21" s="11">
         <v>42</v>
       </c>
-      <c r="Q21" s="14" t="n">
+      <c r="Q21" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="1" t="n">
-        <v>2564</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G22" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H22" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="P22" s="12" t="n">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C22" s="5"/>
+      <c r="D22" s="5"/>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="H22" s="6"/>
+      <c r="P22" s="11">
         <v>46</v>
       </c>
-      <c r="Q22" s="14" t="n">
+      <c r="Q22" s="13">
         <v>4</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="1" t="n">
-        <v>8561</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D23" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" s="1" t="n">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="5"/>
+      <c r="P23" s="11">
         <v>52</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P23" s="12" t="n">
-        <v>52</v>
-      </c>
-      <c r="Q23" s="14" t="n">
+      <c r="Q23" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" s="1" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G24" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P24" s="12" t="n">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="5"/>
+      <c r="P24" s="11">
         <v>56</v>
       </c>
-      <c r="Q24" s="14" t="n">
+      <c r="Q24" s="13">
         <v>2</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B25" s="1" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G25" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="H25" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P25" s="12" t="n">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="5"/>
+      <c r="P25" s="11">
         <v>58</v>
       </c>
-      <c r="Q25" s="13" t="n">
+      <c r="Q25" s="12">
         <v>2</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="1" t="n">
-        <v>6574</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G26" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="H26" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="P26" s="15" t="s">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="H26" s="6"/>
+      <c r="P26" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="Q26" s="16" t="n">
+      <c r="Q26" s="15">
         <v>100</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B27" s="1" t="n">
-        <v>5555</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G27" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B28" s="1" t="n">
-        <v>6125</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G28" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B29" s="1" t="n">
-        <v>5412</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G29" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H29" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B30" s="1" t="n">
-        <v>3256</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G30" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="1" t="n">
-        <v>3264</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G31" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B32" s="1" t="n">
-        <v>4569</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H32" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="1" t="n">
-        <v>7521</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B34" s="1" t="n">
-        <v>6458</v>
-      </c>
-      <c r="C34" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F34" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G34" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B35" s="1" t="n">
-        <v>7569</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G35" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B36" s="1" t="n">
-        <v>8514</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E36" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G36" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B37" s="1" t="n">
-        <v>8563</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E37" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F37" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G37" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H37" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="1" t="n">
-        <v>8642</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E38" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G38" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B39" s="1" t="n">
-        <v>9536</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G39" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="H39" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B40" s="1" t="n">
-        <v>2567</v>
-      </c>
-      <c r="C40" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G40" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B41" s="1" t="n">
-        <v>2154</v>
-      </c>
-      <c r="C41" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H41" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B42" s="1" t="n">
-        <v>3265</v>
-      </c>
-      <c r="C42" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" s="1" t="n">
-        <v>8765</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G43" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" s="1" t="n">
-        <v>3259</v>
-      </c>
-      <c r="C44" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F44" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G44" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H44" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" s="1" t="n">
-        <v>3567</v>
-      </c>
-      <c r="C45" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G45" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="H45" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="1" t="n">
-        <v>6540</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G46" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="1" t="n">
-        <v>2654</v>
-      </c>
-      <c r="C47" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G47" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="H47" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" s="1" t="n">
-        <v>6525</v>
-      </c>
-      <c r="C48" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G48" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="1" t="n">
-        <v>3265</v>
-      </c>
-      <c r="C49" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G49" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="H49" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" s="1" t="n">
-        <v>3265</v>
-      </c>
-      <c r="C50" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E50" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F50" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G50" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="H50" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" s="1" t="n">
-        <v>6125</v>
-      </c>
-      <c r="C51" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G51" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H51" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" s="1" t="n">
-        <v>1562</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G52" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="H52" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" s="1" t="n">
-        <v>1582</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G53" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="H53" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" s="1" t="n">
-        <v>2587</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G54" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="H54" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" s="1" t="n">
-        <v>3549</v>
-      </c>
-      <c r="C55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E55" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F55" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G55" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="H55" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" s="1" t="n">
-        <v>2468</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E56" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F56" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="H56" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" s="1" t="n">
-        <v>2554</v>
-      </c>
-      <c r="C57" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E57" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F57" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H57" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="1" t="n">
-        <v>3598</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="E58" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F58" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="1" t="n">
-        <v>56</v>
-      </c>
-      <c r="H58" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="n">
-        <v>58</v>
-      </c>
-      <c r="B59" s="1" t="n">
-        <v>2456</v>
-      </c>
-      <c r="C59" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="E59" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F59" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G59" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="H59" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="60" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="1" t="n">
-        <v>6548</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E60" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F60" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G60" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="H60" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" s="1" t="n">
-        <v>5486</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G61" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" s="1" t="n">
-        <v>1258</v>
-      </c>
-      <c r="C62" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="E62" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F62" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G62" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="H62" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" s="1" t="n">
-        <v>2579</v>
-      </c>
-      <c r="C63" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="E63" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F63" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G63" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" s="1" t="n">
-        <v>3256</v>
-      </c>
-      <c r="C64" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="E64" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F64" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G64" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="H64" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" s="1" t="n">
-        <v>2587</v>
-      </c>
-      <c r="C65" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D65" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="E65" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F65" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G65" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H65" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="B66" s="1" t="n">
-        <v>3259</v>
-      </c>
-      <c r="C66" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D66" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E66" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F66" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G66" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="H66" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" s="1" t="n">
-        <v>1546</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F67" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G67" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H67" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="1" t="n">
-        <v>3579</v>
-      </c>
-      <c r="C68" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="E68" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F68" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G68" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="n">
-        <v>68</v>
-      </c>
-      <c r="B69" s="1" t="n">
-        <v>6597</v>
-      </c>
-      <c r="C69" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D69" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E69" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F69" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G69" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H69" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="n">
-        <v>69</v>
-      </c>
-      <c r="B70" s="1" t="n">
-        <v>9654</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D70" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E70" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G70" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="B71" s="1" t="n">
-        <v>3569</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="E71" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F71" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G71" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="H71" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="n">
-        <v>71</v>
-      </c>
-      <c r="B72" s="1" t="n">
-        <v>2564</v>
-      </c>
-      <c r="C72" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D72" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E72" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F72" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G72" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H72" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="n">
-        <v>72</v>
-      </c>
-      <c r="B73" s="1" t="n">
-        <v>8561</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="E73" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F73" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="1" t="n">
-        <v>52</v>
-      </c>
-      <c r="H73" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="B74" s="1" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C74" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="E74" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F74" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G74" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="H74" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="n">
-        <v>74</v>
-      </c>
-      <c r="B75" s="1" t="n">
-        <v>5489</v>
-      </c>
-      <c r="C75" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D75" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="E75" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F75" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G75" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="H75" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="B76" s="1" t="n">
-        <v>6574</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G76" s="1" t="n">
-        <v>21</v>
-      </c>
-      <c r="H76" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="n">
-        <v>76</v>
-      </c>
-      <c r="B77" s="1" t="n">
-        <v>5555</v>
-      </c>
-      <c r="C77" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D77" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="E77" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F77" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G77" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H77" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="n">
-        <v>77</v>
-      </c>
-      <c r="B78" s="1" t="n">
-        <v>6125</v>
-      </c>
-      <c r="C78" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D78" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E78" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F78" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G78" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H78" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="B79" s="1" t="n">
-        <v>5412</v>
-      </c>
-      <c r="C79" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D79" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="E79" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F79" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G79" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="H79" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="n">
-        <v>79</v>
-      </c>
-      <c r="B80" s="1" t="n">
-        <v>3256</v>
-      </c>
-      <c r="C80" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="D80" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="E80" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F80" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G80" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="H80" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="1" t="n">
-        <v>3264</v>
-      </c>
-      <c r="C81" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D81" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="E81" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F81" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G81" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H81" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="1" t="n">
-        <v>4569</v>
-      </c>
-      <c r="C82" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G82" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H82" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="1" t="n">
-        <v>7521</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="E83" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F83" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G83" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="H83" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="1" t="n">
-        <v>6458</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F84" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="G84" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H84" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="1" t="n">
-        <v>7569</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="E85" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F85" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G85" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="H85" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="1" t="n">
-        <v>8514</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="E86" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F86" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G86" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="H86" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="1" t="n">
-        <v>8563</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E87" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F87" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G87" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H87" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="1" t="n">
-        <v>8642</v>
-      </c>
-      <c r="C88" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D88" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="E88" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F88" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G88" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="1" t="n">
-        <v>9536</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D89" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="E89" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G89" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="H89" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="90" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="1" t="n">
-        <v>2567</v>
-      </c>
-      <c r="C90" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="D90" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F90" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G90" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="H90" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="1" t="n">
-        <v>2154</v>
-      </c>
-      <c r="C91" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D91" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H91" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="1" t="n">
-        <v>3265</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="D92" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="93" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="1" t="n">
-        <v>8765</v>
-      </c>
-      <c r="C93" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D93" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G93" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="H93" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>3259</v>
-      </c>
-      <c r="C94" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="D94" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="G94" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="H94" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>3567</v>
-      </c>
-      <c r="C95" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D95" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G95" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="H95" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="96" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>6540</v>
-      </c>
-      <c r="C96" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="D96" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G96" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>2654</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="E97" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F97" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G97" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="H97" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>6525</v>
-      </c>
-      <c r="C98" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D98" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="E98" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F98" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G98" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="H98" s="6" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="1" t="n">
-        <v>3265</v>
-      </c>
-      <c r="C99" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="E99" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F99" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G99" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="H99" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="100" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>3265</v>
-      </c>
-      <c r="C100" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E100" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F100" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G100" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="H100" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="101" customFormat="false" ht="14.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="1" t="n">
-        <v>6125</v>
-      </c>
-      <c r="C101" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E101" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="F101" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G101" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="H101" s="6" t="s">
-        <v>18</v>
-      </c>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C29" s="5"/>
+      <c r="D29" s="5"/>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="H29" s="6"/>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C30" s="5"/>
+      <c r="D30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C31" s="5"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.45">
+      <c r="C32" s="5"/>
+      <c r="D32" s="5"/>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="H32" s="6"/>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C33" s="5"/>
+      <c r="D33" s="5"/>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C34" s="5"/>
+      <c r="D34" s="5"/>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C35" s="5"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C36" s="5"/>
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="H37" s="6"/>
+    </row>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C38" s="5"/>
+      <c r="D38" s="5"/>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C39" s="5"/>
+      <c r="D39" s="5"/>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C40" s="5"/>
+      <c r="D40" s="5"/>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C41" s="5"/>
+      <c r="D41" s="5"/>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="H41" s="6"/>
+    </row>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C42" s="5"/>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C43" s="5"/>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C44" s="5"/>
+      <c r="D44" s="5"/>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="H44" s="6"/>
+    </row>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C45" s="5"/>
+      <c r="D45" s="5"/>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C46" s="5"/>
+      <c r="D46" s="5"/>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C47" s="5"/>
+      <c r="D47" s="5"/>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="H47" s="6"/>
+    </row>
+    <row r="48" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C48" s="5"/>
+      <c r="D48" s="5"/>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C49" s="5"/>
+      <c r="D49" s="5"/>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C50" s="5"/>
+      <c r="D50" s="5"/>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="H50" s="6"/>
+    </row>
+    <row r="51" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C51" s="5"/>
+      <c r="D51" s="5"/>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="H52" s="6"/>
+    </row>
+    <row r="53" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C54" s="5"/>
+      <c r="D54" s="5"/>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C55" s="5"/>
+      <c r="D55" s="5"/>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="H55" s="6"/>
+    </row>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C57" s="5"/>
+      <c r="D57" s="5"/>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C58" s="5"/>
+      <c r="D58" s="5"/>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="H58" s="6"/>
+    </row>
+    <row r="59" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C60" s="5"/>
+      <c r="D60" s="5"/>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C61" s="5"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C62" s="5"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C63" s="5"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="H63" s="6"/>
+    </row>
+    <row r="64" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C64" s="5"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C65" s="5"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C66" s="5"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C67" s="5"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C68" s="5"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="H68" s="6"/>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C69" s="5"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C70" s="5"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C71" s="5"/>
+      <c r="D71" s="5"/>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="H72" s="6"/>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C73" s="5"/>
+      <c r="D73" s="5"/>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C74" s="5"/>
+      <c r="D74" s="5"/>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C75" s="5"/>
+      <c r="D75" s="5"/>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C76" s="5"/>
+      <c r="D76" s="5"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="H76" s="6"/>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C77" s="5"/>
+      <c r="D77" s="5"/>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C78" s="5"/>
+      <c r="D78" s="5"/>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C79" s="5"/>
+      <c r="D79" s="5"/>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="H79" s="6"/>
+    </row>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C80" s="5"/>
+      <c r="D80" s="5"/>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="H80" s="5"/>
+    </row>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C81" s="5"/>
+      <c r="D81" s="5"/>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C82" s="5"/>
+      <c r="D82" s="5"/>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="H82" s="6"/>
+    </row>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C83" s="5"/>
+      <c r="D83" s="5"/>
+      <c r="E83" s="5"/>
+      <c r="F83" s="5"/>
+      <c r="H83" s="5"/>
+    </row>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C84" s="5"/>
+      <c r="D84" s="5"/>
+      <c r="E84" s="5"/>
+      <c r="F84" s="5"/>
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C85" s="5"/>
+      <c r="D85" s="5"/>
+      <c r="E85" s="5"/>
+      <c r="F85" s="5"/>
+      <c r="H85" s="5"/>
+    </row>
+    <row r="86" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C86" s="5"/>
+      <c r="D86" s="5"/>
+      <c r="E86" s="5"/>
+      <c r="F86" s="5"/>
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C87" s="5"/>
+      <c r="D87" s="5"/>
+      <c r="E87" s="5"/>
+      <c r="F87" s="5"/>
+      <c r="H87" s="6"/>
+    </row>
+    <row r="88" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C88" s="5"/>
+      <c r="D88" s="5"/>
+      <c r="E88" s="5"/>
+      <c r="F88" s="5"/>
+      <c r="H88" s="5"/>
+    </row>
+    <row r="89" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C89" s="5"/>
+      <c r="D89" s="5"/>
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C90" s="5"/>
+      <c r="D90" s="5"/>
+      <c r="E90" s="5"/>
+      <c r="F90" s="5"/>
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C91" s="5"/>
+      <c r="D91" s="5"/>
+      <c r="E91" s="5"/>
+      <c r="F91" s="5"/>
+      <c r="H91" s="6"/>
+    </row>
+    <row r="92" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C92" s="5"/>
+      <c r="D92" s="5"/>
+      <c r="E92" s="5"/>
+      <c r="F92" s="5"/>
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C93" s="5"/>
+      <c r="D93" s="5"/>
+      <c r="E93" s="5"/>
+      <c r="F93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C94" s="5"/>
+      <c r="D94" s="5"/>
+      <c r="E94" s="5"/>
+      <c r="F94" s="5"/>
+      <c r="H94" s="6"/>
+    </row>
+    <row r="95" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C95" s="5"/>
+      <c r="D95" s="5"/>
+      <c r="E95" s="5"/>
+      <c r="F95" s="5"/>
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C96" s="5"/>
+      <c r="D96" s="5"/>
+      <c r="E96" s="5"/>
+      <c r="F96" s="5"/>
+      <c r="H96" s="5"/>
+    </row>
+    <row r="97" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C97" s="5"/>
+      <c r="D97" s="5"/>
+      <c r="E97" s="5"/>
+      <c r="F97" s="5"/>
+      <c r="H97" s="6"/>
+    </row>
+    <row r="98" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C98" s="5"/>
+      <c r="D98" s="5"/>
+      <c r="E98" s="5"/>
+      <c r="F98" s="5"/>
+      <c r="H98" s="5"/>
+    </row>
+    <row r="99" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C99" s="5"/>
+      <c r="D99" s="5"/>
+      <c r="E99" s="5"/>
+      <c r="F99" s="5"/>
+      <c r="H99" s="5"/>
+    </row>
+    <row r="100" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C100" s="5"/>
+      <c r="D100" s="5"/>
+      <c r="E100" s="5"/>
+      <c r="F100" s="5"/>
+      <c r="H100" s="6"/>
+    </row>
+    <row r="101" spans="3:8" x14ac:dyDescent="0.45">
+      <c r="C101" s="5"/>
+      <c r="D101" s="5"/>
+      <c r="E101" s="5"/>
+      <c r="F101" s="5"/>
+      <c r="H101" s="5"/>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" firstPageNumber="1" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <phoneticPr fontId="5"/>
+  <pageMargins left="0.78749999999999998" right="0.78749999999999998" top="1.05277777777778" bottom="1.05277777777778" header="0.78749999999999998" footer="0.78749999999999998"/>
+  <pageSetup paperSize="9" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter>
     <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId4"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95653b52-df9b-47d2-8549-8de78ac04e21}" enabled="1" method="Standard" siteId="{deff24bb-2089-4400-8c8e-f71e680378b2}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>